--- a/data5.xlsx
+++ b/data5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myrepos\R-Hyphothesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AA4ED8-FD96-4CA8-AA5E-642F1E7FC010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B40E95-C798-47CE-BC54-5DF941C9310B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3696" yWindow="2460" windowWidth="8052" windowHeight="8892" xr2:uid="{9319F6A2-DF05-48AC-84AF-7300389DD8A5}"/>
   </bookViews>

--- a/data5.xlsx
+++ b/data5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myrepos\R-Hyphothesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B40E95-C798-47CE-BC54-5DF941C9310B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7902B6C0-4CAB-473A-84FC-505D2A1B0F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3696" yWindow="2460" windowWidth="8052" windowHeight="8892" xr2:uid="{9319F6A2-DF05-48AC-84AF-7300389DD8A5}"/>
   </bookViews>
